--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486408_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486408_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.514799999999999</v>
+        <v>9.339499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7753</v>
+        <v>8.4459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7395</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>7.156</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3563</v>
+        <v>0.4684</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0144</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3287</v>
+        <v>0.4828</v>
       </c>
       <c r="V2" t="n">
         <v>3.0202</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1194</v>
+        <v>6.919</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7237</v>
+        <v>5.2767</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3957</v>
+        <v>1.6423</v>
       </c>
       <c r="G3" t="n">
         <v>4.5264</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.723</v>
+        <v>1.5225</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9542</v>
+        <v>0.5071</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7688</v>
+        <v>1.0154</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4618</v>
+        <v>6.0206</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1988</v>
+        <v>3.7576</v>
       </c>
       <c r="F4" t="n">
         <v>2.263</v>
@@ -766,10 +766,10 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2536</v>
+        <v>0.3052</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U4" t="n">
         <v>0.4999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.359</v>
+        <v>5.8446</v>
       </c>
       <c r="E5" t="n">
-        <v>4.063</v>
+        <v>4.7335</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2961</v>
+        <v>1.1111</v>
       </c>
       <c r="G5" t="n">
         <v>4.2183</v>
@@ -844,13 +844,13 @@
         <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4694</v>
+        <v>0.0162</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0839</v>
+        <v>-0.4134</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6145</v>
+        <v>0.4296</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.871</v>
+        <v>5.0231</v>
       </c>
       <c r="E6" t="n">
-        <v>2.283</v>
+        <v>3.0653</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5879</v>
+        <v>1.9578</v>
       </c>
       <c r="G6" t="n">
         <v>2.2681</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4624</v>
+        <v>0.6898</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1094</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2105</v>
+        <v>0.5804</v>
       </c>
       <c r="V6" t="n">
         <v>0.7602</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6793</v>
+        <v>1.0789</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5936</v>
+        <v>-0.0019</v>
       </c>
       <c r="F7" t="n">
-        <v>3.273</v>
+        <v>1.0809</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3713</v>
+        <v>-0.9202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4805</v>
+        <v>0.7389</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8518</v>
+        <v>-1.6591</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7091</v>
+        <v>-0.03</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5776</v>
+        <v>0.6752</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1314</v>
+        <v>-0.7052</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3378</v>
+        <v>-0.8902</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0582</v>
+        <v>0.0636</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7204</v>
+        <v>-0.9539</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6602</v>
+        <v>1.0866</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0523</v>
+        <v>0.2031</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6079</v>
+        <v>0.8835</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.5443</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5625</v>
+        <v>-0.0606</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6725</v>
+        <v>-2.717</v>
       </c>
       <c r="F8" t="n">
-        <v>1.235</v>
+        <v>2.6565</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9202</v>
+        <v>-0.3713</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7389</v>
+        <v>0.4805</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6591</v>
+        <v>-0.8518</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03</v>
+        <v>-0.7091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6752</v>
+        <v>-0.5776</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7052</v>
+        <v>-0.1314</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8902</v>
+        <v>0.3378</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0636</v>
+        <v>1.0582</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9539</v>
+        <v>-0.7204</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5702</v>
+        <v>1.9203</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0377</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1653</v>
+        <v>-0.6286</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9767</v>
+        <v>1.3062</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8114</v>
+        <v>-1.9347</v>
       </c>
       <c r="G9" t="n">
         <v>1.5004</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1423</v>
+        <v>0.3485</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8736</v>
+        <v>0.2031</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2687</v>
+        <v>0.1454</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5597</v>
+        <v>-3.3632</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.155</v>
+        <v>-1.2668</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4047</v>
+        <v>-2.0964</v>
       </c>
       <c r="G10" t="n">
         <v>0.4316</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4915</v>
+        <v>-0.295</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1286</v>
+        <v>0.0168</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6201</v>
+        <v>-0.3118</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6297</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>30.1734</v>
+        <v>30.1733</v>
       </c>
       <c r="E11" t="n">
-        <v>22.5994</v>
+        <v>22.5995</v>
       </c>
       <c r="F11" t="n">
         <v>7.5741</v>
@@ -1315,10 +1315,10 @@
         <v>6.0625</v>
       </c>
       <c r="T11" t="n">
-        <v>1.345899999999999</v>
+        <v>1.3459</v>
       </c>
       <c r="U11" t="n">
-        <v>4.716600000000001</v>
+        <v>4.7166</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9139000000000002</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3177</v>
+        <v>0.6516</v>
       </c>
       <c r="E12" t="n">
         <v>-0.1712</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4889</v>
+        <v>0.8229</v>
       </c>
       <c r="G12" t="n">
         <v>0.8469</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.6303</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6218</v>
+        <v>-0.2878</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1524</v>
+        <v>-0.7108</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3288</v>
+        <v>0.4347</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1764</v>
+        <v>-1.1456</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3018</v>
@@ -1468,13 +1468,13 @@
         <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2367</v>
+        <v>0.3734</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2161</v>
+        <v>0.3221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.094</v>
+        <v>-0.8217</v>
       </c>
       <c r="E14" t="n">
         <v>-0.3224</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7716</v>
+        <v>-0.4993</v>
       </c>
       <c r="G14" t="n">
         <v>-3.0816</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1423</v>
+        <v>-0.87</v>
       </c>
       <c r="T14" t="n">
         <v>-0.6729000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4694</v>
+        <v>-0.1971</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4503</v>
+        <v>-1.3836</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6349</v>
+        <v>0.173</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.0852</v>
+        <v>-1.5566</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3819</v>
+        <v>-1.5557</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2743</v>
+        <v>-1.131</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1076</v>
+        <v>-0.4247</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3542</v>
+        <v>1.1019</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4417</v>
+        <v>-1.4441</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9125</v>
+        <v>2.546</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-2.6576</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1674</v>
+        <v>0.3131</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.9707</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7023</v>
+        <v>-1.1329</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.262</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4403</v>
+        <v>-0.204</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8486</v>
+        <v>-1.5736</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0505</v>
+        <v>1.6349</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7981</v>
+        <v>-3.2085</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5557</v>
+        <v>2.3819</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.131</v>
+        <v>1.2743</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4247</v>
+        <v>1.1076</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1019</v>
+        <v>3.3542</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4441</v>
+        <v>1.4417</v>
       </c>
       <c r="L16" t="n">
-        <v>2.546</v>
+        <v>1.9125</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6576</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3131</v>
+        <v>-0.1674</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.9707</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5979</v>
+        <v>-0.8256</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1524</v>
+        <v>-0.262</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4455</v>
+        <v>-0.5636</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9167</v>
+        <v>-1.7408</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3881</v>
+        <v>-0.0202</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3048</v>
+        <v>-1.7206</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0672</v>
+        <v>-2.8559</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7663</v>
+        <v>-0.6478</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8335</v>
+        <v>-2.2081</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6965</v>
+        <v>0.3628</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5147</v>
+        <v>-0.2309</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1818</v>
+        <v>0.5937</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7637</v>
+        <v>-3.2187</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7484</v>
+        <v>-0.4169</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.0153</v>
+        <v>-2.8018</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5445</v>
+        <v>-0.7544</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1334</v>
+        <v>-0.4254</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4111</v>
+        <v>-0.329</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.8695</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2628</v>
+        <v>-1.7511</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4511</v>
+        <v>1.2763</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.7138</v>
+        <v>-3.0274</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8569</v>
+        <v>-0.0672</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3985</v>
+        <v>0.7663</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.4584</v>
+        <v>-0.8335</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5403</v>
+        <v>3.6965</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0151</v>
+        <v>1.5147</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5554</v>
+        <v>2.1818</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.3972</v>
+        <v>-3.7637</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3834</v>
+        <v>-0.7484</v>
       </c>
       <c r="O18" t="n">
-        <v>-4.0138</v>
+        <v>-3.0153</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1438</v>
+        <v>-0.3788</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2824</v>
+        <v>-0.2451</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1385</v>
+        <v>-0.1337</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2806</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4131</v>
+        <v>-2.3668</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4218</v>
+        <v>1.5628</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0087</v>
+        <v>-3.9296</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2671</v>
+        <v>-3.8569</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5292</v>
+        <v>-0.3985</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2621</v>
+        <v>-3.4584</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5738</v>
+        <v>0.5403</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7268</v>
+        <v>-0.0151</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>0.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3067</v>
+        <v>-4.3972</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1976</v>
+        <v>-0.3834</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1091</v>
+        <v>-4.0138</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.233</v>
+        <v>-0.2478</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.1706</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4399</v>
+        <v>-0.0772</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3904</v>
+        <v>1.5204</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2806</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3904</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7504</v>
+        <v>-2.5415</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6907</v>
+        <v>-3.4218</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0596</v>
+        <v>0.8803</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8559</v>
+        <v>-0.2671</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6478</v>
+        <v>-0.5292</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2081</v>
+        <v>0.2621</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3628</v>
+        <v>-0.5738</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2309</v>
+        <v>-0.7268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5937</v>
+        <v>0.153</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2187</v>
+        <v>0.3067</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4169</v>
+        <v>0.1976</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.8018</v>
+        <v>0.1091</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.764</v>
+        <v>-0.3614</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0959</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.668</v>
+        <v>0.3115</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8695</v>
+        <v>-0.3904</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7395</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3957</v>
+        <v>-4.6975</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9269</v>
+        <v>-3.0387</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4688</v>
+        <v>-1.6588</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8336</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0479</v>
+        <v>-0.2539</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6934</v>
+        <v>-0.8051</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7413</v>
+        <v>0.5513</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9942</v>
+        <v>-6.1709</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9459</v>
+        <v>-2.6239</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0484</v>
+        <v>-3.5471</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.8182</v>
+        <v>-3.4408</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9949</v>
+        <v>-0.4653</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.8233</v>
+        <v>-2.9755</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9374</v>
+        <v>-1.1434</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.429</v>
+        <v>-0.3983</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5084</v>
+        <v>-0.7451</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8808</v>
+        <v>-2.2974</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5659</v>
+        <v>-0.067</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3149</v>
+        <v>-2.2304</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2792</v>
+        <v>-0.1875</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.3929</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2876</v>
+        <v>0.2055</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5177</v>
+        <v>-6.3218</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8474</v>
+        <v>-3.0576</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6704</v>
+        <v>-3.2641</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4408</v>
+        <v>-5.8182</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4653</v>
+        <v>-1.9949</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9755</v>
+        <v>-3.8233</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1434</v>
+        <v>-2.9374</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3983</v>
+        <v>-1.429</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7451</v>
+        <v>-1.5084</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2974</v>
+        <v>-2.8808</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.067</v>
+        <v>-0.5659</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2304</v>
+        <v>-2.3149</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5343</v>
+        <v>-0.0484</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.1202</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0822</v>
+        <v>0.0718</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8902</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8902</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-30.17339999999999</v>
+        <v>-29.4285</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.5739</v>
+        <v>-7.5741</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.5995</v>
+        <v>-21.8544</v>
       </c>
       <c r="G24" t="n">
         <v>-22.85</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.195599999999999</v>
+        <v>-8.195600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-14.6544</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6747</v>
+        <v>2.674699999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-5.274100000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>7.948800000000001</v>
+        <v>7.9488</v>
       </c>
       <c r="M24" t="n">
         <v>-25.5247</v>
@@ -2323,25 +2323,25 @@
         <v>-11.9628</v>
       </c>
       <c r="R24" t="n">
-        <v>9.787500000000001</v>
+        <v>9.787499999999998</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.0625</v>
+        <v>-5.3176</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.716600000000001</v>
+        <v>-4.7164</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3461</v>
+        <v>-0.6009</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9141000000000004</v>
+        <v>0.9141000000000001</v>
       </c>
       <c r="W24" t="n">
         <v>6.4307</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.5167</v>
+        <v>-5.516699999999999</v>
       </c>
     </row>
   </sheetData>
